--- a/database/test.xlsx
+++ b/database/test.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ZP-List" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'ZP-List'!$A$1:$AH$10</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'ZP-List'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -1236,6 +1236,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$AH$10"/>
+  <autoFilter ref="$A$1:$I$25"/>
 </worksheet>
 </file>
--- a/database/test.xlsx
+++ b/database/test.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ZP-List" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'ZP-List'!$A$1:$I$25</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'ZP-List'!$A$1:$AH$10</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -1236,6 +1236,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$I$25"/>
+  <autoFilter ref="$A$1:$AH$10"/>
 </worksheet>
 </file>